--- a/artfynd/A 72934-2021 artfynd.xlsx
+++ b/artfynd/A 72934-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72934-2021 artfynd.xlsx
+++ b/artfynd/A 72934-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66489977</v>
+        <v>66489965</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403032.295189716</v>
+        <v>402558</v>
       </c>
       <c r="R2" t="n">
-        <v>7015987.024779269</v>
+        <v>7015768</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66489964</v>
+        <v>66489963</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402853.192815437</v>
+        <v>402865</v>
       </c>
       <c r="R3" t="n">
-        <v>7015853.632154428</v>
+        <v>7015863</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,21 +845,11 @@
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +861,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,16 +882,11 @@
         <v>66489966</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402532.9434265065</v>
+        <v>402533</v>
       </c>
       <c r="R4" t="n">
-        <v>7015724.062212823</v>
+        <v>7015724</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +947,9 @@
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-06-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66489963</v>
+        <v>66489967</v>
       </c>
       <c r="B5" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402865.213475162</v>
+        <v>402456</v>
       </c>
       <c r="R5" t="n">
-        <v>7015863.18338877</v>
+        <v>7015714</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,21 +1049,11 @@
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,7 +1065,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66489965</v>
+        <v>66489977</v>
       </c>
       <c r="B6" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402558.2015632667</v>
+        <v>403032</v>
       </c>
       <c r="R6" t="n">
-        <v>7015768.362887654</v>
+        <v>7015987</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,21 +1151,11 @@
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1242,7 +1167,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1263,16 +1188,11 @@
         <v>66489978</v>
       </c>
       <c r="B7" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402986.976355982</v>
+        <v>402987</v>
       </c>
       <c r="R7" t="n">
-        <v>7016010.470195548</v>
+        <v>7016010</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,19 +1253,9 @@
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2010-06-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66489967</v>
+        <v>66489964</v>
       </c>
       <c r="B8" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402455.9157516392</v>
+        <v>402853</v>
       </c>
       <c r="R8" t="n">
-        <v>7015713.776633956</v>
+        <v>7015854</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1450,21 +1355,11 @@
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2010-06-11</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1476,7 +1371,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 72934-2021 artfynd.xlsx
+++ b/artfynd/A 72934-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66489965</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66489963</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66489966</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66489967</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66489977</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66489978</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,8 +1421,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66489964</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>